--- a/data_lake/industry/TrendForce/TFT LCD.xlsx
+++ b/data_lake/industry/TrendForce/TFT LCD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79E6C3B-815D-2748-A324-DCC344A61DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E340A986-CA90-144A-AD3A-1749B669690B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17460" yWindow="780" windowWidth="18540" windowHeight="20700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="37">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -1154,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
@@ -1593,6 +1593,44 @@
         <v>6.2</v>
       </c>
     </row>
+    <row r="11" spans="1:25">
+      <c r="A11" s="10">
+        <v>46265</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C11" s="11">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="F11" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="G11" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="H11" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="I11" s="13">
+        <v>5.7</v>
+      </c>
+      <c r="J11" s="13">
+        <v>8.5</v>
+      </c>
+      <c r="K11" s="13">
+        <v>6.2</v>
+      </c>
+      <c r="L11" s="13">
+        <v>6.2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -1607,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="10" bestFit="1" customWidth="1"/>
@@ -2402,6 +2440,80 @@
       </c>
       <c r="X11" s="13">
         <v>172.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25">
+      <c r="A12" s="10">
+        <v>46265</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46265</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="13">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="F12" s="13">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G12" s="13">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="H12" s="13">
+        <v>75.7</v>
+      </c>
+      <c r="I12" s="13">
+        <v>98.8</v>
+      </c>
+      <c r="J12" s="13">
+        <v>141.4</v>
+      </c>
+      <c r="K12" s="13">
+        <v>100.2</v>
+      </c>
+      <c r="L12" s="13">
+        <v>100.2</v>
+      </c>
+      <c r="M12" s="13">
+        <v>210</v>
+      </c>
+      <c r="N12" s="13">
+        <v>334.6</v>
+      </c>
+      <c r="O12" s="13">
+        <v>294.8</v>
+      </c>
+      <c r="P12" s="13">
+        <v>292.7</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>394.3</v>
+      </c>
+      <c r="R12" s="13">
+        <v>455.9</v>
+      </c>
+      <c r="S12" s="13">
+        <v>419.1</v>
+      </c>
+      <c r="T12" s="13">
+        <v>416.5</v>
+      </c>
+      <c r="U12" s="13">
+        <v>156.9</v>
+      </c>
+      <c r="V12" s="13">
+        <v>230</v>
+      </c>
+      <c r="W12" s="13">
+        <v>178.3</v>
+      </c>
+      <c r="X12" s="13">
+        <v>172.5</v>
       </c>
     </row>
   </sheetData>
